--- a/feedback_forms/001_faculty_student_partnership_attitudes_survey--feedback_forms.xlsx
+++ b/feedback_forms/001_faculty_student_partnership_attitudes_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,38 +520,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>faculty_survey</t>
+          <t>faculty_partnership</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Faculty Survey</t>
+          <t>Faculty Partnership</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>student_survey</t>
+          <t>student_collaboration</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Student Survey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Student Collaboration</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How often do you engage in collaborative research projects with students?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,17 +565,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>faculty_survey_2</t>
+          <t>satisfaction_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faculty Survey 2</t>
+          <t>Satisfaction with Support</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +588,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>student_survey_2</t>
+          <t>comfort_technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Student Survey 2</t>
+          <t>Comfort with Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -612,15 +616,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>faculty_survey_3</t>
+          <t>projects_last_year</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faculty Survey 3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Projects in Last Year</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How many research projects have you collaborated with students on in the past academic year?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,18 +643,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>faculty_survey_3_1</t>
+          <t>office_hours_importance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Faculty Survey 3</t>
+          <t>Importance of Office Hours</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,64 +666,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>faculty_survey_3_2</t>
+          <t>funded_projects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faculty Survey 3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Funded Projects</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Have you ever participated in a faculty-student collaborative project that received funding or recognition?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>faculty_survey_3_3</t>
+          <t>number_of_students</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faculty Survey 3</t>
+          <t>Number of Students</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>student_survey_3_1</t>
+          <t>best_aspect</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Student Survey 3</t>
+          <t>Best Aspect of Working with Students</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,38 +739,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>student_survey_3_2</t>
+          <t>feedback_quality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Student Survey 3</t>
+          <t>Feedback Quality</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>student_survey_3_3</t>
+          <t>hours_per_week</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Student Survey 3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Hours per Week</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How many hours per week do you usually dedicate to student-led projects?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,17 +784,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>student_survey_3_3_1</t>
+          <t>department_support</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Student Survey 3</t>
+          <t>Department Support</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,46 +807,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>faculty_survey_4</t>
+          <t>funding_source</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faculty Survey 4</t>
+          <t>Funding Source</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>faculty_survey_4_1</t>
+          <t>collaboration_tools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faculty Survey 4</t>
+          <t>Collaboration Tools</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,41 +858,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>faculty_survey_4_2</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faculty Survey 4</t>
+          <t>Job Satisfaction</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>faculty_survey_4_3</t>
+          <t>recognition_frequency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faculty Survey 4</t>
+          <t>Recognition Frequency</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -888,35 +904,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>student_survey_4_1</t>
+          <t>autonomy_in_decision</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Student Survey 4</t>
+          <t>Autonomy in Decision-Making</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>student_survey_4_2</t>
+          <t>mentorship_relationship</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Student Survey 4</t>
+          <t>Mentorship Relationship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,23 +945,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>faculty_survey_5</t>
+          <t>mentorship_quality</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faculty Survey 5</t>
+          <t>Mentorship Quality</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -957,64 +973,64 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>faculty_survey_5_1</t>
+          <t>mentees_last_year</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faculty Survey 5</t>
+          <t>Number of Mentees Last Year</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>faculty_survey_5_1_1</t>
+          <t>student_services_quality</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faculty Survey 5</t>
+          <t>Student Services Quality</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>student_survey_5</t>
+          <t>advice_from_students</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Student Survey 5</t>
+          <t>Advice from Students</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1042,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>student_survey_5_1</t>
+          <t>job_satisfaction_when_working_with_students</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Student Survey 5</t>
+          <t>Job Satisfaction When Working with Students</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1049,39 +1065,108 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>faculty_survey_6</t>
+          <t>facilities_resources</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faculty Survey 6</t>
+          <t>Facilities and Resources</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>faculty_survey_6_1</t>
+          <t>student_feedback_on_my_work</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faculty Survey 6</t>
+          <t>Student Feedback on My Work</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>diversity_in_projects</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Diversity in Projects</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>departmental_support</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Departmental Support</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>feedback_from_students</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Feedback from Students</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +1183,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,663 +1211,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>faculty_survey_2_choices</t>
+          <t>student_collaboration_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>faculty_survey_2_choices</t>
+          <t>student_collaboration_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>faculty_survey_2_choices</t>
+          <t>student_collaboration_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_survey_2_choices</t>
+          <t>student_collaboration_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>student_survey_2_choices</t>
+          <t>student_collaboration_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>student_survey_2_choices</t>
+          <t>office_hours_importance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>faculty_survey_3_1_choices</t>
+          <t>office_hours_importance_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>faculty_survey_3_1_choices</t>
+          <t>office_hours_importance_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>faculty_survey_3_1_choices</t>
+          <t>office_hours_importance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not at All Important</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_survey_3_1_choices</t>
+          <t>department_support_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_survey_3_1_choices</t>
+          <t>department_support_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>student_survey_3_1_choices</t>
+          <t>department_support_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>student_survey_3_3_choices</t>
+          <t>department_support_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>student_survey_3_3_choices</t>
+          <t>department_support_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not at All Satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>student_survey_3_3_choices</t>
+          <t>departmental_support_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>student_survey_3_3_1_choices</t>
+          <t>departmental_support_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>student_survey_3_3_1_choices</t>
+          <t>departmental_support_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>student_survey_3_3_1_choices</t>
+          <t>departmental_support_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>faculty_survey_4_choices</t>
+          <t>departmental_support_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not at All Satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>faculty_survey_4_choices</t>
+          <t>feedback_from_students_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>faculty_survey_4_choices</t>
+          <t>feedback_from_students_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>faculty_survey_4_3_choices</t>
+          <t>feedback_from_students_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>faculty_survey_4_3_choices</t>
+          <t>feedback_from_students_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>faculty_survey_4_3_choices</t>
+          <t>feedback_from_students_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>student_survey_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>student_survey_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>student_survey_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>faculty_survey_5_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>student_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>student_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>student_survey_5_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>faculty_survey_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>faculty_survey_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>faculty_survey_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Not at All Satisfied</t>
         </is>
       </c>
     </row>
